--- a/ig/175-upgrade-app-profiles/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/175-upgrade-app-profiles/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-14T10:16:17+00:00</t>
+    <t>2024-02-14T11:10:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
